--- a/data/trans_bre/IQ26A_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IQ26A_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 2,43</t>
+          <t>-11,22; 1,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 1,4</t>
+          <t>-12,07; 1,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 12,19</t>
+          <t>-1,54; 12,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,65</t>
+          <t>0,0; 28,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 194,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-91,37; 60,04</t>
+          <t>-88,88; 83,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-59,6; 1218,27</t>
+          <t>-55,9; 1101,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,99</t>
+          <t>8,96</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>199,6%</t>
+          <t>216,09%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 12,12</t>
+          <t>-1,17; 13,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 12,12</t>
+          <t>-4,56; 11,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 10,9</t>
+          <t>-9,78; 11,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 23,47</t>
+          <t>-2,48; 23,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 223,51</t>
+          <t>-14,13; 244,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 124,05</t>
+          <t>-26,46; 113,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 51,55</t>
+          <t>-31,07; 54,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,55; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,36</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 9,73</t>
+          <t>-10,3; 11,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 3,52</t>
+          <t>-5,15; 3,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 26,48</t>
+          <t>3,43; 28,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,49; 73,77</t>
+          <t>-49,3; 87,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-9,57</t>
+          <t>-17,65</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-24,67%</t>
+          <t>-39,46%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 10,12</t>
+          <t>-6,81; 10,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 1,44</t>
+          <t>-18,79; 1,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 2,5</t>
+          <t>-19,29; 2,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,71; 27,31</t>
+          <t>-56,64; 21,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,31; 193,44</t>
+          <t>-55,21; 202,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,5; 13,55</t>
+          <t>-67,28; 10,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,07; 16,35</t>
+          <t>-62,49; 15,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,61; 246,77</t>
+          <t>-85,1; 165,74</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,91</t>
+          <t>17,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 7,03</t>
+          <t>-4,88; 6,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 11,07</t>
+          <t>-11,31; 10,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,46</t>
+          <t>0,0; 16,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 46,7</t>
+          <t>-12,52; 44,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 180,57</t>
+          <t>-74,53; 170,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 107,88</t>
+          <t>-15,99; 101,09</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>4,36</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>166,96%</t>
+          <t>133,13%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 19,32</t>
+          <t>0,22; 19,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 9,56</t>
+          <t>-1,38; 10,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 6,49</t>
+          <t>-6,78; 6,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 30,56</t>
+          <t>-6,35; 27,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 513,47</t>
+          <t>-10,08; 485,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 6063488,19</t>
+          <t>-100,0; 7012548,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 6,76</t>
+          <t>-6,76; 7,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,55</t>
+          <t>-2,9; 5,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 11,3</t>
+          <t>-6,94; 11,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 30,6</t>
+          <t>-13,62; 28,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-40,31; 63,52</t>
+          <t>-38,24; 63,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-55,71; 223,57</t>
+          <t>-51,89; 202,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 55,35</t>
+          <t>-23,75; 54,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 88,27</t>
+          <t>-24,93; 80,78</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-4,42</t>
+          <t>-4,74</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 6,48</t>
+          <t>-7,26; 6,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 5,86</t>
+          <t>-7,76; 5,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 2,9</t>
+          <t>-7,93; 2,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 0,0</t>
+          <t>-16,61; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,58; 44,64</t>
+          <t>-34,35; 44,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,38; 41,74</t>
+          <t>-37,41; 45,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-55,52; 34,52</t>
+          <t>-57,55; 31,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,51</t>
+          <t>-1,48; 4,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,18</t>
+          <t>-3,18; 2,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,97</t>
+          <t>-2,61; 3,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 14,41</t>
+          <t>-2,84; 13,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 41,51</t>
+          <t>-11,54; 41,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 22,75</t>
+          <t>-25,0; 27,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 23,99</t>
+          <t>-16,69; 27,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 95,36</t>
+          <t>-13,09; 91,52</t>
         </is>
       </c>
     </row>
